--- a/aarsplan-matematik-2026-27.xlsx
+++ b/aarsplan-matematik-2026-27.xlsx
@@ -1541,7 +1541,7 @@
       <c r="C36" s="43" t="n"/>
       <c r="D36" s="43" t="inlineStr">
         <is>
-          <t>Repetition, prøvetræning og forløbet Chokolade. Uge 20: lejrskole på Bornholm.</t>
+          <t>Repetition og prøvetræning. Uge 20: lejrskole på Bornholm.</t>
         </is>
       </c>
       <c r="E36" s="33" t="n"/>

--- a/aarsplan-matematik-2026-27.xlsx
+++ b/aarsplan-matematik-2026-27.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Årsplan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projektopgave" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Årsplan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Overblik" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Projektopgave" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Årsplan'!$4:$4</definedName>
@@ -701,7 +701,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="28">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -1595,7 +1594,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="28">
       <c r="A3" s="45" t="inlineStr">
         <is>
@@ -1688,8 +1686,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="28">
       <c r="A11" s="50" t="inlineStr">
         <is>
@@ -1769,8 +1765,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="28">
       <c r="A20" s="50" t="inlineStr">
         <is>
@@ -1832,14 +1826,14 @@
     <row r="1" ht="17.35" customHeight="1" s="28">
       <c r="A1" s="44" t="inlineStr">
         <is>
-          <t>Projektopgaven i 9. klasse · plads til datoer</t>
+          <t>OPO i 9. klasse · uge 4, 5 og 6</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="28">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>Ugenumrene herunder er ikke fastlagt endnu. Skriv dem ind, når skolens plan ligger fast — så flytter jeg forløbene i årsplanen, hvis de kolliderer.</t>
+          <t>Ugenumrene er fastlagt til 4, 5 og 6. Plan revideres når vi nærmer os.</t>
         </is>
       </c>
     </row>

--- a/aarsplan-matematik-2026-27.xlsx
+++ b/aarsplan-matematik-2026-27.xlsx
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="27" min="1" max="1"/>
@@ -1428,138 +1428,158 @@
       <c r="G31" s="39" t="n"/>
     </row>
     <row r="32" ht="39" customHeight="1" s="28">
-      <c r="A32" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="B32" s="36" t="inlineStr">
-        <is>
-          <t>25.01 - 29.01</t>
-        </is>
-      </c>
-      <c r="C32" s="36" t="inlineStr">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>Uge 4 - 6</t>
+        </is>
+      </c>
+      <c r="B32" s="41" t="n"/>
+      <c r="C32" s="41" t="n"/>
+      <c r="D32" s="41" t="inlineStr">
+        <is>
+          <t>OPO — obligatorisk projektopgave, ingen matematikundervisning</t>
+        </is>
+      </c>
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="33" t="n"/>
+      <c r="G32" s="34" t="n"/>
+    </row>
+    <row r="33" ht="39" customHeight="1" s="28">
+      <c r="A33" s="40" t="inlineStr">
+        <is>
+          <t>Uge 7</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="n"/>
+      <c r="C33" s="41" t="n"/>
+      <c r="D33" s="41" t="inlineStr">
+        <is>
+          <t>Vinterferie</t>
+        </is>
+      </c>
+      <c r="E33" s="33" t="n"/>
+      <c r="F33" s="33" t="n"/>
+      <c r="G33" s="34" t="n"/>
+    </row>
+    <row r="34" ht="33.75" customHeight="1" s="28">
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B34" s="36" t="inlineStr">
+        <is>
+          <t>22.02 - 26.02</t>
+        </is>
+      </c>
+      <c r="C34" s="36" t="inlineStr">
         <is>
           <t>Geometri og måling</t>
         </is>
       </c>
-      <c r="D32" s="37" t="inlineStr">
+      <c r="D34" s="37" t="inlineStr">
         <is>
           <t>Tegn med mål</t>
         </is>
       </c>
-      <c r="E32" s="38" t="inlineStr">
+      <c r="E34" s="38" t="inlineStr">
         <is>
           <t>Konstruere præcise todimensionelle tegninger i GeoGebra
 Konstruere tegninger med målestoksforhold
 Identificere hvilke oplysninger der er nødvendige for at fremstille en given tegning</t>
         </is>
       </c>
-      <c r="F32" s="38" t="n"/>
-      <c r="G32" s="39" t="n"/>
-    </row>
-    <row r="33" ht="39" customHeight="1" s="28">
-      <c r="A33" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" s="36" t="inlineStr">
-        <is>
-          <t>01.02 - 05.02</t>
-        </is>
-      </c>
-      <c r="C33" s="36" t="inlineStr">
+      <c r="F34" s="38" t="n"/>
+      <c r="G34" s="39" t="n"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="1" s="28">
+      <c r="A35" s="35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="inlineStr">
+        <is>
+          <t>01.03 - 05.03</t>
+        </is>
+      </c>
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>Geometri og måling</t>
         </is>
       </c>
-      <c r="D33" s="37" t="inlineStr">
+      <c r="D35" s="37" t="inlineStr">
         <is>
           <t>Mål på flader</t>
         </is>
       </c>
-      <c r="E33" s="38" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Bestemme areal og omkreds af komplekse figurer med digitale værktøjer
 Dele en kompleks figur op i kendte figurer
 Anvende formler for areal og omkreds samt Pythagoras</t>
         </is>
       </c>
-      <c r="F33" s="38" t="n"/>
-      <c r="G33" s="39" t="n"/>
-    </row>
-    <row r="34" ht="33.75" customHeight="1" s="28">
-      <c r="A34" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" s="36" t="inlineStr">
-        <is>
-          <t>08.02 - 12.02</t>
-        </is>
-      </c>
-      <c r="C34" s="36" t="inlineStr">
+    </row>
+    <row r="36" ht="19.5" customHeight="1" s="28">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" s="36" t="inlineStr">
+        <is>
+          <t>08.03 - 12.03</t>
+        </is>
+      </c>
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>Geometri og måling</t>
         </is>
       </c>
-      <c r="D34" s="37" t="inlineStr">
+      <c r="D36" s="37" t="inlineStr">
         <is>
           <t>Rumfang og vægt</t>
         </is>
       </c>
-      <c r="E34" s="38" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Beregne rumfanget af bl.a. keglestubbe og pyramidestubbe
 Bestemme massefylde, vægt og rumfang af genstande fra hverdagen</t>
         </is>
       </c>
-      <c r="F34" s="38" t="n"/>
-      <c r="G34" s="39" t="n"/>
-    </row>
-    <row r="35" ht="19.5" customHeight="1" s="28">
-      <c r="A35" s="42" t="inlineStr">
-        <is>
-          <t>Uge 7 - 8</t>
-        </is>
-      </c>
-      <c r="B35" s="43" t="n"/>
-      <c r="C35" s="43" t="n"/>
-      <c r="D35" s="43" t="inlineStr">
-        <is>
-          <t>Vinterferie uge 7/8 — kernestoffet er kørt igennem her</t>
-        </is>
-      </c>
-      <c r="E35" s="33" t="n"/>
-      <c r="F35" s="33" t="n"/>
-      <c r="G35" s="34" t="n"/>
-    </row>
-    <row r="36" ht="19.5" customHeight="1" s="28">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>Uge 8 - 19</t>
-        </is>
-      </c>
-      <c r="B36" s="43" t="n"/>
-      <c r="C36" s="43" t="n"/>
-      <c r="D36" s="43" t="inlineStr">
-        <is>
-          <t>Repetition og prøvetræning. Uge 20: lejrskole på Bornholm.</t>
-        </is>
-      </c>
-      <c r="E36" s="33" t="n"/>
-      <c r="F36" s="33" t="n"/>
-      <c r="G36" s="34" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>Uge 11 - 19</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="n"/>
+      <c r="C37" s="43" t="n"/>
+      <c r="D37" s="43" t="inlineStr">
+        <is>
+          <t>Repetition og prøvetræning; kernestoffet er kørt igennem her. Uge 20: lejrskole på Bornholm.</t>
+        </is>
+      </c>
+      <c r="E37" s="33" t="n"/>
+      <c r="F37" s="33" t="n"/>
+      <c r="G37" s="34" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D37:G37"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="D14:G14"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="D32:G32"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="G6:G10 G12:G13 G15 G17:G20 G22:G26 G29:G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
@@ -1579,7 +1599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="27" min="1" max="1"/>
@@ -1732,69 +1752,82 @@
     <row r="15" ht="15" customHeight="1" s="28">
       <c r="A15" s="51" t="inlineStr">
         <is>
-          <t>Uge 7 - 8</t>
+          <t>Uge 4 - 6</t>
         </is>
       </c>
       <c r="B15" s="52" t="inlineStr">
         <is>
-          <t>Vinterferie</t>
+          <t>OPO — obligatorisk projektopgave</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="28">
       <c r="A16" s="51" t="inlineStr">
         <is>
-          <t>Uge 12</t>
+          <t>Uge 7</t>
         </is>
       </c>
       <c r="B16" s="52" t="inlineStr">
         <is>
-          <t>Påskeferie</t>
+          <t>Vinterferie</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="28">
       <c r="A17" s="51" t="inlineStr">
         <is>
+          <t>Uge 12</t>
+        </is>
+      </c>
+      <c r="B17" s="52" t="inlineStr">
+        <is>
+          <t>Påskeferie</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
           <t>Uge 20</t>
         </is>
       </c>
-      <c r="B17" s="52" t="inlineStr">
+      <c r="B18" s="52" t="inlineStr">
         <is>
           <t>Lejrskole på Bornholm</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="28">
-      <c r="A20" s="50" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="28"/>
+    <row r="21" ht="15" customHeight="1" s="28">
+      <c r="A21" s="50" t="inlineStr">
         <is>
           <t>Sådan bruger du arket</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="28">
-      <c r="A21" s="53" t="inlineStr">
-        <is>
-          <t>· Gule felter i kolonnen Noter / status er dine. Der er en rulleliste med Ikke planlagt, Planlagt, I gang og Afsluttet.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="28">
       <c r="A22" s="53" t="inlineStr">
         <is>
-          <t>· Alle andre felter kan frit rettes — skriv bare over dem.</t>
+          <t>· Gule felter i kolonnen Noter / status er dine. Der er en rulleliste med Ikke planlagt, Planlagt, I gang og Afsluttet.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="28">
       <c r="A23" s="53" t="inlineStr">
         <is>
-          <t>· Vil du flytte et forløb, skift ugenummer og periode, og træk rækken op eller ned.</t>
+          <t>· Alle andre felter kan frit rettes — skriv bare over dem.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="28">
       <c r="A24" s="53" t="inlineStr">
+        <is>
+          <t>· Vil du flytte et forløb, skift ugenummer og periode, og træk rækken op eller ned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="53" t="inlineStr">
         <is>
           <t>· Tælleren herover opdaterer sig selv, når du ændrer blokken i kolonne C på Årsplan-arket.</t>
         </is>
@@ -1837,7 +1870,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="28">
       <c r="A4" s="45" t="inlineStr">
         <is>

--- a/aarsplan-matematik-2026-27.xlsx
+++ b/aarsplan-matematik-2026-27.xlsx
@@ -697,7 +697,7 @@
     <row r="2" ht="15" customHeight="1" s="28">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>Kernestoffet er fordelt på uge 33 til uge 6, så alle forløb er kørt igennem inden vinterferien. Uge 8 og frem er sat af til repetition og prøvetræning.</t>
+          <t>Kernestoffet er fordelt på uge 33 til uge 10. Uge 4 til 6 er OPO, og uge 7 er vinterferie, så de tre sidste geometriforløb ligger i uge 8, 9 og 10. Uge 11 og frem er sat af til repetition og prøvetræning.</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
           <t>Mål på flader</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="27" t="inlineStr">
         <is>
           <t>Bestemme areal og omkreds af komplekse figurer med digitale værktøjer
 Dele en kompleks figur op i kendte figurer
@@ -1542,7 +1542,7 @@
           <t>Rumfang og vægt</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>Beregne rumfanget af bl.a. keglestubbe og pyramidestubbe
 Bestemme massefylde, vægt og rumfang af genstande fra hverdagen</t>
